--- a/Kalla_Aspal Scraper.xlsx
+++ b/Kalla_Aspal Scraper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Repository\kalla-aspal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1DFABD-39EB-49BB-883C-B7829520DD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6C543E-2423-4F76-AC3B-2672DCCD350B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="412">
   <si>
     <t>Pengawasan Rekonstruksi Jalan DBH Sawit</t>
   </si>
@@ -824,349 +824,439 @@
     <t>Pembangunan Trotoar Jl. Sutan Syahrir Kec. Pontianak Kota</t>
   </si>
   <si>
+    <t>Penandatanganan Kontrak</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142522000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pelebaran Jl. Petani Kec. Pontianak Kota (Lanjutan)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142524000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jl. Amali Kec. Pontianak Tenggara (Lanjutan)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142526000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jl. Abu Naim Kec. Pontianak Timur</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142529000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jl. Tekam Kec. Pontianak Timur (Lanjutan)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142530000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jl. Selat Panjang II Kec. Pontianak Utara (Lanjutan)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142531000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pembangunan Jl. Tanjung Raya II (Jl. Penghubung Pemda) Kec. Pontianak Timur (Lanjutan)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10142535000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jalan Tanjungpura Jl. Tanjungpura-Desa Pesaguan Kanan-Desa Harapan Baru)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10142536000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10145101000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10145137000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsultan Pengawas Peningkatan Ruas Jalan Sp. Buluh Kuning – Ng. Libau</t>
+  </si>
+  <si>
+    <t>sintang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/sintang/lelang/10148328000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Ruas Jalan Sp. Buluh Kuning – Ng. Libau</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/sintang/lelang/10148330000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10148514000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10148519000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10149054000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10149056000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10149312000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Rehabilitasi Gedung Olahraga Rehabilitasi Gedung Olahraga Stadion Opu Daeng Manambon Spesifikasi: Jl. Pangsuma, Desa Antibar, Kecamatan Mempawah Timur (BANKEU)</t>
+  </si>
+  <si>
+    <t>mempawahkab</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/mempawahkab/lelang/10151597000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152013000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jalan Karya Bersama Jalan Lingkar Kendawangan) Kec. Kendawangan</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152254000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Peningkatan Jalan S. Parman (Trotoar)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152256000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152257000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Jalan Zainudin Kec. Sandai</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152261000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Jl. Pramuka Kec. Sandai</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152264000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pemeliharaan Jalan Kabupaten</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10152336000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10153996000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROVINSI KALIMANTAN BARAT WILAYAH III (KONDISI ASPAL)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10154362000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Jalan Lingkar GOR Stadion Opu Daeng Manambon Spesifikasi: Jl. Pangsuma, Desa Antibar, Kecamatan Mempawah Timur (BANKEU)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/mempawahkab/lelang/10154696000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN BUNYAU - SERAWAI (KONDISI NON ASPAL)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10154716000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN UPT PJJ WILAYAH I (KLASTER I TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10155537000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN UPT PJJ WILAYAH I (KLASTER II TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10155538000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROVINSI KALIMANTAN BARAT (WILAYAH IV)</t>
+  </si>
+  <si>
     <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga</t>
   </si>
   <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142522000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pelebaran Jl. Petani Kec. Pontianak Kota (Lanjutan)</t>
-  </si>
-  <si>
-    <t>Penandatanganan Kontrak</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142524000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jl. Amali Kec. Pontianak Tenggara (Lanjutan)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142526000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jl. Abu Naim Kec. Pontianak Timur</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142529000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jl. Tekam Kec. Pontianak Timur (Lanjutan)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142530000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jl. Selat Panjang II Kec. Pontianak Utara (Lanjutan)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142531000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pembangunan Jl. Tanjung Raya II (Jl. Penghubung Pemda) Kec. Pontianak Timur (Lanjutan)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10142535000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jalan Tanjungpura Jl. Tanjungpura-Desa Pesaguan Kanan-Desa Harapan Baru)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10142536000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10145101000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10145137000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsultan Pengawas Peningkatan Ruas Jalan Sp. Buluh Kuning – Ng. Libau</t>
-  </si>
-  <si>
-    <t>sintang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/sintang/lelang/10148328000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Ruas Jalan Sp. Buluh Kuning – Ng. Libau</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/sintang/lelang/10148330000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10148514000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10148519000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10149054000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10149056000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10149312000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Rehabilitasi Gedung Olahraga Rehabilitasi Gedung Olahraga Stadion Opu Daeng Manambon Spesifikasi: Jl. Pangsuma, Desa Antibar, Kecamatan Mempawah Timur (BANKEU)</t>
-  </si>
-  <si>
-    <t>mempawahkab</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/mempawahkab/lelang/10151597000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152013000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jalan Karya Bersama Jalan Lingkar Kendawangan) Kec. Kendawangan</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152254000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Peningkatan Jalan S. Parman (Trotoar)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152256000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152257000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Jalan Zainudin Kec. Sandai</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152261000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Jl. Pramuka Kec. Sandai</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152264000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pemeliharaan Jalan Kabupaten</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10152336000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10153996000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROVINSI KALIMANTAN BARAT WILAYAH III (KONDISI ASPAL)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10154362000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Jalan Lingkar GOR Stadion Opu Daeng Manambon Spesifikasi: Jl. Pangsuma, Desa Antibar, Kecamatan Mempawah Timur (BANKEU)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/mempawahkab/lelang/10154696000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN BUNYAU - SERAWAI (KONDISI NON ASPAL)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10154716000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN UPT PJJ WILAYAH I (KLASTER I TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10155537000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN UPT PJJ WILAYAH I (KLASTER II TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10155538000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROVINSI KALIMANTAN BARAT (WILAYAH IV)</t>
-  </si>
-  <si>
     <t>https://spse.inaproc.id/kalbarprov/lelang/10155652000/pengumumanlelang</t>
   </si>
   <si>
     <t>Penggantian Jembatan Jl. Tanggul Kec. Pontianak Barat</t>
   </si>
   <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10156342000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsultan Perencanaan Pemeliharaan Berkala Jalan TA. 2027</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10156350000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsultan Perencanaan Peningkatan Jalan APBD TA. 2027</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10156355000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsultan Perencanaan Pembangunan Jalan TA. 2027</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10156357000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsultan Perencanaan Pelebaran Jalan Menuju Standar TA. 2027</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/pontianak/lelang/10156360000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10157537000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsolidasi Rekonstruksi Jalan Teluk Empening - Permata dan Rehabilitasi Jalan Teluk Empening - Permata</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10158889000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsolidasi Rekonstruksi Jalan Radak Dua - Terentang Hulu dan Rehabilitasi Jalan Radak Dua - Terentang Hulu</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10158890000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Konsolidasi Rekonstruksi Jalan Terentang Hilir - Radak Satu dan Rehabilitasi Jalan Terentang Hilir - Radak Satu</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10158940000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Rehabilitasi Jalan Sungai Kakap - Jeruju Besar</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10159231000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PENGGANTIAN/PEMBANGUNAN JEMBATAN RUAS JALAN PESAGUAN – KENDAWANGAN</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10159762000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/ketapangkab/lelang/10159805000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pembangunan Bangunan Perkuatan Tebing Jl. Raden Adinata Desa Sejegi Kab. Mempawah</t>
+  </si>
+  <si>
+    <t>Pengumuman Pascakualifikasi [...]</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10159926000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pembangunan Bangunan Perkuatan Tebing Jl. Gst. Haidir Desa Antibar</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10160245000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Surat Penunjukan Penyedia Barang/Jasa [...]</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10160843000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Penguatan Database dan Survey Kondisi Jalan dan Jembatan</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kapuashulukab/lelang/10161082000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pembangunan Jalan Masuk Sekolah Rakyat</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/mempawahkab/lelang/10163091000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10163117000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Survey Kondisi Jalan Kabupaten</t>
+  </si>
+  <si>
+    <t>Seleksi Gagal</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10163967000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10164342000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Tidak Ada Jadwal</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10164811000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kuburayakab/lelang/10164924000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Jl. Parit Kebayan Ds. Jungkat</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/mempawahkab/lelang/10165680000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER I TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10166700000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER II TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10166704000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER III TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10166707000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER IV TERSEBAR)</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10166709000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Rekonstruksi Jalan Ruas Suka Maju - Banyu Abang (DBH Sawit 2026)</t>
+  </si>
+  <si>
+    <t>kayongutarakab</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kayongutarakab/lelang/10166717000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Pengumuman Pemenang [...]</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/mempawahkab/lelang/10167675000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PENGAWASAN TEKNIS PEMELIHARAAN BERKALA JALAN YA’ M. SABRAN (SIMPANG SULTAN HAMID II - TUGU ALIANYANG)</t>
+  </si>
+  <si>
+    <t>Masa Sanggah Prakualifikasi</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168176000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) JALAN DAN JEMBATAN RUAS JALAN TEBIDAH - BUNYAU - SERAWAI DAN RUAS JALAN SEMUBUK - SINTANG</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168225000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) JALAN MARAU - AIR UPAS</t>
+  </si>
+  <si>
+    <t>Evaluasi Dokumen Kualifikasi</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168229000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) JALAN DAN JEMBATAN RUAS JALAN KEMBAYAN - BALAI SEBUT - BALAI SEPUAK DAN KOTA BARU - NANGA SOKAN</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168231000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) JALAN DAN JEMBATAN RUAS JALAN SUKADANA - TELUK BATANG</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168532000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) JALAN DAN JEMBATAN RUAS JALAN TUMBANG TITI - TANJUNG DAN RUAS JALAN SIMPANG SEI. GANTANG - TELUK BATU</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168534000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PERENCANAAN TEKNIS (DED) PENANGANAN LONGSORAN RUAS JALAN KEMBAYAN - BALAI SEBUT</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10168572000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10169802000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10169804000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10170979000/pengumumanlelang</t>
+  </si>
+  <si>
     <t>Masa Sanggah</t>
   </si>
   <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10156342000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsultan Perencanaan Pemeliharaan Berkala Jalan TA. 2027</t>
-  </si>
-  <si>
-    <t>Download Dokumen Pemilihan [...]</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10156350000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsultan Perencanaan Peningkatan Jalan APBD TA. 2027</t>
-  </si>
-  <si>
-    <t>Pembukaan dan Evaluasi Penawaran File II: Harga</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10156355000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsultan Perencanaan Pembangunan Jalan TA. 2027</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10156357000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsultan Perencanaan Pelebaran Jalan Menuju Standar TA. 2027</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/pontianak/lelang/10156360000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Surat Penunjukan Penyedia Barang/Jasa [...]</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10157537000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsolidasi Rekonstruksi Jalan Teluk Empening - Permata dan Rehabilitasi Jalan Teluk Empening - Permata</t>
-  </si>
-  <si>
-    <t>Surat Penunjukan Penyedia Barang/Jasa</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10158889000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsolidasi Rekonstruksi Jalan Radak Dua - Terentang Hulu dan Rehabilitasi Jalan Radak Dua - Terentang Hulu</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10158890000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Konsolidasi Rekonstruksi Jalan Terentang Hilir - Radak Satu dan Rehabilitasi Jalan Terentang Hilir - Radak Satu</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10158940000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Rehabilitasi Jalan Sungai Kakap - Jeruju Besar</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10159231000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PENGGANTIAN/PEMBANGUNAN JEMBATAN RUAS JALAN PESAGUAN – KENDAWANGAN</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10159762000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/ketapangkab/lelang/10159805000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pembangunan Bangunan Perkuatan Tebing Jl. Raden Adinata Desa Sejegi Kab. Mempawah</t>
-  </si>
-  <si>
-    <t>Pengumuman Pascakualifikasi [...]</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10159926000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pembangunan Bangunan Perkuatan Tebing Jl. Gst. Haidir Desa Antibar</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10160245000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10160843000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Penguatan Database dan Survey Kondisi Jalan dan Jembatan</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kapuashulukab/lelang/10161082000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Pembangunan Jalan Masuk Sekolah Rakyat</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/mempawahkab/lelang/10163091000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10163117000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Survey Kondisi Jalan Kabupaten</t>
-  </si>
-  <si>
-    <t>Seleksi Gagal</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10163967000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10164342000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Masa Sanggah Prakualifikasi</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10164811000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga [...]</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kuburayakab/lelang/10164924000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER I TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10166700000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER II TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10166704000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER III TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10166707000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>PEMELIHARAAN RUTIN JALAN PROV. KALBAR WILAYAH II (KLASTER IV TERSEBAR)</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kalbarprov/lelang/10166709000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>Rekonstruksi Jalan Ruas Suka Maju - Banyu Abang (DBH Sawit 2026)</t>
-  </si>
-  <si>
-    <t>kayongutarakab</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/kayongutarakab/lelang/10166717000/pengumumanlelang</t>
-  </si>
-  <si>
-    <t>https://spse.inaproc.id/mempawahkab/lelang/10167675000/pengumumanlelang</t>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10170980000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>PENGAWASAN TEKNIS PEMELIHARAAN BERKALA JALAN SEI RAYA DALAM I, JALAN IMAM BONJOL DAN JALAN ADI SUCIPTO</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10171293000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>https://spse.inaproc.id/kalbarprov/lelang/10174153000/pengumumanlelang</t>
+  </si>
+  <si>
+    <t>Nama Paket</t>
+  </si>
+  <si>
+    <t>Wilayah</t>
+  </si>
+  <si>
+    <t>Jenis</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>HPS</t>
+  </si>
+  <si>
+    <t>Due date</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -1182,15 +1272,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1198,12 +1294,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1493,16 +1605,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A5:H194"/>
+  <dimension ref="A4:H208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="163" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.88671875" customWidth="1"/>
     <col min="5" max="5" width="46.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="68.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
@@ -4923,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F136">
         <v>999400000</v>
@@ -4932,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="H136" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -4940,7 +5075,7 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C137" t="s">
         <v>87</v>
@@ -4958,7 +5093,7 @@
         <v>4</v>
       </c>
       <c r="H137" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
@@ -4966,7 +5101,7 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C138" t="s">
         <v>87</v>
@@ -4975,7 +5110,7 @@
         <v>18</v>
       </c>
       <c r="E138" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F138">
         <v>3000000000</v>
@@ -4984,7 +5119,7 @@
         <v>4</v>
       </c>
       <c r="H138" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
@@ -4992,7 +5127,7 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C139" t="s">
         <v>87</v>
@@ -5001,7 +5136,7 @@
         <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F139">
         <v>999400000</v>
@@ -5010,7 +5145,7 @@
         <v>4</v>
       </c>
       <c r="H139" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
@@ -5018,7 +5153,7 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C140" t="s">
         <v>87</v>
@@ -5027,7 +5162,7 @@
         <v>18</v>
       </c>
       <c r="E140" t="s">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F140">
         <v>2000000000</v>
@@ -5036,7 +5171,7 @@
         <v>4</v>
       </c>
       <c r="H140" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -5044,7 +5179,7 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C141" t="s">
         <v>87</v>
@@ -5053,7 +5188,7 @@
         <v>18</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="F141">
         <v>3000000000</v>
@@ -5062,7 +5197,7 @@
         <v>4</v>
       </c>
       <c r="H141" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
@@ -5070,7 +5205,7 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C142" t="s">
         <v>160</v>
@@ -5088,7 +5223,7 @@
         <v>4</v>
       </c>
       <c r="H142" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -5114,7 +5249,7 @@
         <v>4</v>
       </c>
       <c r="H143" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
@@ -5140,7 +5275,7 @@
         <v>4</v>
       </c>
       <c r="H144" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
@@ -5148,10 +5283,10 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
+        <v>285</v>
+      </c>
+      <c r="C145" t="s">
         <v>286</v>
-      </c>
-      <c r="C145" t="s">
-        <v>287</v>
       </c>
       <c r="D145" t="s">
         <v>2</v>
@@ -5166,7 +5301,7 @@
         <v>4</v>
       </c>
       <c r="H145" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
@@ -5174,10 +5309,10 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C146" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D146" t="s">
         <v>18</v>
@@ -5192,7 +5327,7 @@
         <v>4</v>
       </c>
       <c r="H146" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
@@ -5218,7 +5353,7 @@
         <v>4</v>
       </c>
       <c r="H147" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -5244,7 +5379,7 @@
         <v>4</v>
       </c>
       <c r="H148" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
@@ -5270,7 +5405,7 @@
         <v>4</v>
       </c>
       <c r="H149" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
@@ -5296,7 +5431,7 @@
         <v>4</v>
       </c>
       <c r="H150" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
@@ -5322,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="H151" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
@@ -5330,16 +5465,16 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
+        <v>295</v>
+      </c>
+      <c r="C152" t="s">
         <v>296</v>
       </c>
-      <c r="C152" t="s">
-        <v>297</v>
-      </c>
       <c r="D152" t="s">
         <v>18</v>
       </c>
       <c r="E152" t="s">
-        <v>267</v>
+        <v>3</v>
       </c>
       <c r="F152">
         <v>2900000000</v>
@@ -5348,7 +5483,7 @@
         <v>4</v>
       </c>
       <c r="H152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
@@ -5356,7 +5491,7 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C153" t="s">
         <v>160</v>
@@ -5374,7 +5509,7 @@
         <v>4</v>
       </c>
       <c r="H153" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
@@ -5382,7 +5517,7 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C154" t="s">
         <v>160</v>
@@ -5400,7 +5535,7 @@
         <v>4</v>
       </c>
       <c r="H154" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
@@ -5408,7 +5543,7 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C155" t="s">
         <v>160</v>
@@ -5426,7 +5561,7 @@
         <v>4</v>
       </c>
       <c r="H155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5452,7 +5587,7 @@
         <v>4</v>
       </c>
       <c r="H156" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
@@ -5460,7 +5595,7 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C157" t="s">
         <v>160</v>
@@ -5478,7 +5613,7 @@
         <v>4</v>
       </c>
       <c r="H157" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
@@ -5486,7 +5621,7 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C158" t="s">
         <v>160</v>
@@ -5504,7 +5639,7 @@
         <v>4</v>
       </c>
       <c r="H158" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
@@ -5512,7 +5647,7 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C159" t="s">
         <v>160</v>
@@ -5530,7 +5665,7 @@
         <v>4</v>
       </c>
       <c r="H159" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
@@ -5556,7 +5691,7 @@
         <v>4</v>
       </c>
       <c r="H160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
@@ -5564,7 +5699,7 @@
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C161" t="s">
         <v>101</v>
@@ -5582,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="H161" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
@@ -5590,16 +5725,16 @@
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C162" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D162" t="s">
         <v>18</v>
       </c>
       <c r="E162" t="s">
-        <v>267</v>
+        <v>3</v>
       </c>
       <c r="F162">
         <v>952400000</v>
@@ -5608,7 +5743,7 @@
         <v>4</v>
       </c>
       <c r="H162" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
@@ -5616,7 +5751,7 @@
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C163" t="s">
         <v>101</v>
@@ -5634,7 +5769,7 @@
         <v>4</v>
       </c>
       <c r="H163" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
@@ -5642,7 +5777,7 @@
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C164" t="s">
         <v>101</v>
@@ -5660,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="H164" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
@@ -5668,7 +5803,7 @@
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C165" t="s">
         <v>101</v>
@@ -5686,7 +5821,7 @@
         <v>4</v>
       </c>
       <c r="H165" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
@@ -5694,16 +5829,16 @@
         <v>162</v>
       </c>
       <c r="B166" t="s">
+        <v>321</v>
+      </c>
+      <c r="C166" t="s">
+        <v>101</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="s">
         <v>322</v>
-      </c>
-      <c r="C166" t="s">
-        <v>101</v>
-      </c>
-      <c r="D166" t="s">
-        <v>18</v>
-      </c>
-      <c r="E166" t="s">
-        <v>267</v>
       </c>
       <c r="F166">
         <v>4100000000</v>
@@ -5729,7 +5864,7 @@
         <v>18</v>
       </c>
       <c r="E167" t="s">
-        <v>325</v>
+        <v>3</v>
       </c>
       <c r="F167">
         <v>1500000000</v>
@@ -5738,7 +5873,7 @@
         <v>4</v>
       </c>
       <c r="H167" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
@@ -5746,7 +5881,7 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C168" t="s">
         <v>87</v>
@@ -5755,7 +5890,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="F168">
         <v>568400000</v>
@@ -5764,7 +5899,7 @@
         <v>4</v>
       </c>
       <c r="H168" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
@@ -5772,7 +5907,7 @@
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C169" t="s">
         <v>87</v>
@@ -5781,7 +5916,7 @@
         <v>2</v>
       </c>
       <c r="E169" t="s">
-        <v>331</v>
+        <v>3</v>
       </c>
       <c r="F169">
         <v>635800000</v>
@@ -5790,7 +5925,7 @@
         <v>4</v>
       </c>
       <c r="H169" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
@@ -5798,7 +5933,7 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C170" t="s">
         <v>87</v>
@@ -5807,7 +5942,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>331</v>
+        <v>3</v>
       </c>
       <c r="F170">
         <v>396700000</v>
@@ -5816,7 +5951,7 @@
         <v>4</v>
       </c>
       <c r="H170" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
@@ -5824,7 +5959,7 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C171" t="s">
         <v>87</v>
@@ -5833,7 +5968,7 @@
         <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="F171">
         <v>198700000</v>
@@ -5842,7 +5977,7 @@
         <v>4</v>
       </c>
       <c r="H171" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
@@ -5859,7 +5994,7 @@
         <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>337</v>
+        <v>3</v>
       </c>
       <c r="F172">
         <v>1400000000</v>
@@ -5868,7 +6003,7 @@
         <v>4</v>
       </c>
       <c r="H172" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
@@ -5876,7 +6011,7 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C173" t="s">
         <v>1</v>
@@ -5885,7 +6020,7 @@
         <v>18</v>
       </c>
       <c r="E173" t="s">
-        <v>340</v>
+        <v>3</v>
       </c>
       <c r="F173">
         <v>800000000</v>
@@ -5894,7 +6029,7 @@
         <v>4</v>
       </c>
       <c r="H173" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
@@ -5902,7 +6037,7 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C174" t="s">
         <v>1</v>
@@ -5920,7 +6055,7 @@
         <v>4</v>
       </c>
       <c r="H174" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
@@ -5928,7 +6063,7 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C175" t="s">
         <v>1</v>
@@ -5937,7 +6072,7 @@
         <v>18</v>
       </c>
       <c r="E175" t="s">
-        <v>340</v>
+        <v>3</v>
       </c>
       <c r="F175">
         <v>600000000</v>
@@ -5946,7 +6081,7 @@
         <v>4</v>
       </c>
       <c r="H175" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
@@ -5954,7 +6089,7 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
@@ -5963,7 +6098,7 @@
         <v>18</v>
       </c>
       <c r="E176" t="s">
-        <v>340</v>
+        <v>3</v>
       </c>
       <c r="F176">
         <v>1500000000</v>
@@ -5972,7 +6107,7 @@
         <v>4</v>
       </c>
       <c r="H176" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
@@ -5980,7 +6115,7 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C177" t="s">
         <v>101</v>
@@ -5989,7 +6124,7 @@
         <v>18</v>
       </c>
       <c r="E177" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="F177">
         <v>14100000000</v>
@@ -5998,7 +6133,7 @@
         <v>4</v>
       </c>
       <c r="H177" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
@@ -6006,7 +6141,7 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C178" t="s">
         <v>160</v>
@@ -6024,7 +6159,7 @@
         <v>4</v>
       </c>
       <c r="H178" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
@@ -6032,7 +6167,7 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C179" t="s">
         <v>101</v>
@@ -6041,7 +6176,7 @@
         <v>18</v>
       </c>
       <c r="E179" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F179">
         <v>7800000000</v>
@@ -6050,7 +6185,7 @@
         <v>4</v>
       </c>
       <c r="H179" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
@@ -6058,7 +6193,7 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C180" t="s">
         <v>101</v>
@@ -6067,7 +6202,7 @@
         <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>352</v>
+        <v>3</v>
       </c>
       <c r="F180">
         <v>6400000000</v>
@@ -6076,7 +6211,7 @@
         <v>4</v>
       </c>
       <c r="H180" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
@@ -6084,7 +6219,7 @@
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C181" t="s">
         <v>101</v>
@@ -6093,7 +6228,7 @@
         <v>18</v>
       </c>
       <c r="E181" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="F181">
         <v>3100000000</v>
@@ -6102,7 +6237,7 @@
         <v>4</v>
       </c>
       <c r="H181" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
@@ -6110,7 +6245,7 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C182" t="s">
         <v>98</v>
@@ -6119,7 +6254,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>328</v>
+        <v>3</v>
       </c>
       <c r="F182">
         <v>500900000</v>
@@ -6128,7 +6263,7 @@
         <v>4</v>
       </c>
       <c r="H182" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -6136,10 +6271,10 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C183" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D183" t="s">
         <v>18</v>
@@ -6154,7 +6289,7 @@
         <v>4</v>
       </c>
       <c r="H183" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
@@ -6171,7 +6306,7 @@
         <v>18</v>
       </c>
       <c r="E184" t="s">
-        <v>325</v>
+        <v>3</v>
       </c>
       <c r="F184">
         <v>4000000000</v>
@@ -6180,7 +6315,7 @@
         <v>4</v>
       </c>
       <c r="H184" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
@@ -6188,7 +6323,7 @@
         <v>181</v>
       </c>
       <c r="B185" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C185" t="s">
         <v>1</v>
@@ -6197,7 +6332,7 @@
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F185">
         <v>348900000</v>
@@ -6206,7 +6341,7 @@
         <v>4</v>
       </c>
       <c r="H185" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
@@ -6214,7 +6349,7 @@
         <v>182</v>
       </c>
       <c r="B186" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C186" t="s">
         <v>101</v>
@@ -6223,7 +6358,7 @@
         <v>18</v>
       </c>
       <c r="E186" t="s">
-        <v>325</v>
+        <v>3</v>
       </c>
       <c r="F186">
         <v>4500000000</v>
@@ -6232,7 +6367,7 @@
         <v>4</v>
       </c>
       <c r="H186" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -6240,7 +6375,7 @@
         <v>183</v>
       </c>
       <c r="B187" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C187" t="s">
         <v>1</v>
@@ -6249,7 +6384,7 @@
         <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F187">
         <v>348900000</v>
@@ -6258,7 +6393,7 @@
         <v>4</v>
       </c>
       <c r="H187" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
@@ -6266,7 +6401,7 @@
         <v>184</v>
       </c>
       <c r="B188" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C188" t="s">
         <v>1</v>
@@ -6275,7 +6410,7 @@
         <v>18</v>
       </c>
       <c r="E188" t="s">
-        <v>368</v>
+        <v>3</v>
       </c>
       <c r="F188">
         <v>800000000</v>
@@ -6284,7 +6419,7 @@
         <v>4</v>
       </c>
       <c r="H188" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
@@ -6292,25 +6427,25 @@
         <v>185</v>
       </c>
       <c r="B189" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>296</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
       </c>
       <c r="E189" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F189">
-        <v>1800000000</v>
+        <v>2100000000</v>
       </c>
       <c r="G189" t="s">
-        <v>4</v>
+        <v>366</v>
       </c>
       <c r="H189" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -6318,7 +6453,7 @@
         <v>186</v>
       </c>
       <c r="B190" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C190" t="s">
         <v>101</v>
@@ -6327,16 +6462,16 @@
         <v>18</v>
       </c>
       <c r="E190" t="s">
-        <v>352</v>
+        <v>27</v>
       </c>
       <c r="F190">
-        <v>1600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="G190" t="s">
         <v>4</v>
       </c>
       <c r="H190" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
@@ -6344,7 +6479,7 @@
         <v>187</v>
       </c>
       <c r="B191" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C191" t="s">
         <v>101</v>
@@ -6353,16 +6488,16 @@
         <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>352</v>
+        <v>3</v>
       </c>
       <c r="F191">
-        <v>885100000</v>
+        <v>1600000000</v>
       </c>
       <c r="G191" t="s">
         <v>4</v>
       </c>
       <c r="H191" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
@@ -6370,7 +6505,7 @@
         <v>188</v>
       </c>
       <c r="B192" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C192" t="s">
         <v>101</v>
@@ -6379,16 +6514,16 @@
         <v>18</v>
       </c>
       <c r="E192" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F192">
-        <v>927900000</v>
+        <v>885100000</v>
       </c>
       <c r="G192" t="s">
         <v>4</v>
       </c>
       <c r="H192" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
@@ -6396,25 +6531,25 @@
         <v>189</v>
       </c>
       <c r="B193" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C193" t="s">
-        <v>379</v>
+        <v>101</v>
       </c>
       <c r="D193" t="s">
         <v>18</v>
       </c>
       <c r="E193" t="s">
-        <v>328</v>
+        <v>27</v>
       </c>
       <c r="F193">
-        <v>1800000000</v>
+        <v>927900000</v>
       </c>
       <c r="G193" t="s">
         <v>4</v>
       </c>
       <c r="H193" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
@@ -6422,25 +6557,389 @@
         <v>190</v>
       </c>
       <c r="B194" t="s">
+        <v>376</v>
+      </c>
+      <c r="C194" t="s">
+        <v>377</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="s">
+        <v>267</v>
+      </c>
+      <c r="F194">
+        <v>1800000000</v>
+      </c>
+      <c r="G194" t="s">
+        <v>4</v>
+      </c>
+      <c r="H194" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>191</v>
+      </c>
+      <c r="B195" t="s">
+        <v>355</v>
+      </c>
+      <c r="C195" t="s">
+        <v>296</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" t="s">
+        <v>379</v>
+      </c>
+      <c r="F195">
+        <v>2500000000</v>
+      </c>
+      <c r="G195" t="s">
+        <v>4</v>
+      </c>
+      <c r="H195" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>192</v>
+      </c>
+      <c r="B196" t="s">
+        <v>381</v>
+      </c>
+      <c r="C196" t="s">
+        <v>101</v>
+      </c>
+      <c r="D196" t="s">
+        <v>2</v>
+      </c>
+      <c r="E196" t="s">
+        <v>382</v>
+      </c>
+      <c r="F196">
+        <v>346900000</v>
+      </c>
+      <c r="G196" t="s">
+        <v>366</v>
+      </c>
+      <c r="H196" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>193</v>
+      </c>
+      <c r="B197" t="s">
+        <v>384</v>
+      </c>
+      <c r="C197" t="s">
+        <v>101</v>
+      </c>
+      <c r="D197" t="s">
+        <v>2</v>
+      </c>
+      <c r="E197" t="s">
+        <v>382</v>
+      </c>
+      <c r="F197">
+        <v>450100000</v>
+      </c>
+      <c r="G197" t="s">
+        <v>366</v>
+      </c>
+      <c r="H197" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>194</v>
+      </c>
+      <c r="B198" t="s">
+        <v>386</v>
+      </c>
+      <c r="C198" t="s">
+        <v>101</v>
+      </c>
+      <c r="D198" t="s">
+        <v>2</v>
+      </c>
+      <c r="E198" t="s">
+        <v>387</v>
+      </c>
+      <c r="F198">
+        <v>442600000</v>
+      </c>
+      <c r="G198" t="s">
+        <v>366</v>
+      </c>
+      <c r="H198" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>195</v>
+      </c>
+      <c r="B199" t="s">
+        <v>389</v>
+      </c>
+      <c r="C199" t="s">
+        <v>101</v>
+      </c>
+      <c r="D199" t="s">
+        <v>2</v>
+      </c>
+      <c r="E199" t="s">
+        <v>382</v>
+      </c>
+      <c r="F199">
+        <v>451100000</v>
+      </c>
+      <c r="G199" t="s">
+        <v>366</v>
+      </c>
+      <c r="H199" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>196</v>
+      </c>
+      <c r="B200" t="s">
+        <v>391</v>
+      </c>
+      <c r="C200" t="s">
+        <v>101</v>
+      </c>
+      <c r="D200" t="s">
+        <v>2</v>
+      </c>
+      <c r="E200" t="s">
         <v>359</v>
       </c>
-      <c r="C194" t="s">
-        <v>297</v>
-      </c>
-      <c r="D194" t="s">
-        <v>18</v>
-      </c>
-      <c r="E194" t="s">
-        <v>352</v>
-      </c>
-      <c r="F194">
-        <v>2500000000</v>
-      </c>
-      <c r="G194" t="s">
-        <v>4</v>
-      </c>
-      <c r="H194" t="s">
-        <v>381</v>
+      <c r="F200">
+        <v>246800000</v>
+      </c>
+      <c r="G200" t="s">
+        <v>366</v>
+      </c>
+      <c r="H200" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>197</v>
+      </c>
+      <c r="B201" t="s">
+        <v>393</v>
+      </c>
+      <c r="C201" t="s">
+        <v>101</v>
+      </c>
+      <c r="D201" t="s">
+        <v>206</v>
+      </c>
+      <c r="E201" t="s">
+        <v>359</v>
+      </c>
+      <c r="F201">
+        <v>454300000</v>
+      </c>
+      <c r="G201" t="s">
+        <v>366</v>
+      </c>
+      <c r="H201" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>198</v>
+      </c>
+      <c r="B202" t="s">
+        <v>395</v>
+      </c>
+      <c r="C202" t="s">
+        <v>101</v>
+      </c>
+      <c r="D202" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" t="s">
+        <v>387</v>
+      </c>
+      <c r="F202">
+        <v>245300000</v>
+      </c>
+      <c r="G202" t="s">
+        <v>366</v>
+      </c>
+      <c r="H202" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>199</v>
+      </c>
+      <c r="B203" t="s">
+        <v>393</v>
+      </c>
+      <c r="C203" t="s">
+        <v>101</v>
+      </c>
+      <c r="D203" t="s">
+        <v>2</v>
+      </c>
+      <c r="E203" t="s">
+        <v>382</v>
+      </c>
+      <c r="F203">
+        <v>454300000</v>
+      </c>
+      <c r="G203" t="s">
+        <v>366</v>
+      </c>
+      <c r="H203" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>200</v>
+      </c>
+      <c r="B204" t="s">
+        <v>391</v>
+      </c>
+      <c r="C204" t="s">
+        <v>101</v>
+      </c>
+      <c r="D204" t="s">
+        <v>2</v>
+      </c>
+      <c r="E204" t="s">
+        <v>382</v>
+      </c>
+      <c r="F204">
+        <v>246800000</v>
+      </c>
+      <c r="G204" t="s">
+        <v>366</v>
+      </c>
+      <c r="H204" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>201</v>
+      </c>
+      <c r="B205" t="s">
+        <v>374</v>
+      </c>
+      <c r="C205" t="s">
+        <v>101</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205">
+        <v>927900000</v>
+      </c>
+      <c r="G205" t="s">
+        <v>366</v>
+      </c>
+      <c r="H205" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>202</v>
+      </c>
+      <c r="B206" t="s">
+        <v>368</v>
+      </c>
+      <c r="C206" t="s">
+        <v>101</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" t="s">
+        <v>400</v>
+      </c>
+      <c r="F206">
+        <v>1800000000</v>
+      </c>
+      <c r="G206" t="s">
+        <v>366</v>
+      </c>
+      <c r="H206" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>203</v>
+      </c>
+      <c r="B207" t="s">
+        <v>402</v>
+      </c>
+      <c r="C207" t="s">
+        <v>101</v>
+      </c>
+      <c r="D207" t="s">
+        <v>2</v>
+      </c>
+      <c r="E207" t="s">
+        <v>382</v>
+      </c>
+      <c r="F207">
+        <v>346900000</v>
+      </c>
+      <c r="G207" t="s">
+        <v>366</v>
+      </c>
+      <c r="H207" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>204</v>
+      </c>
+      <c r="B208" t="s">
+        <v>374</v>
+      </c>
+      <c r="C208" t="s">
+        <v>101</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" t="s">
+        <v>347</v>
+      </c>
+      <c r="F208">
+        <v>927900000</v>
+      </c>
+      <c r="G208" t="s">
+        <v>366</v>
+      </c>
+      <c r="H208" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
